--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122489274</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461895</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B5" t="n">
-        <v>90828</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489274</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,6 +795,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461895</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
         <v>6788288</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,29 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122488593</v>
+        <v>122489274</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1009,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1016,7 +1031,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461988</v>
+        <v>461895</v>
       </c>
       <c r="R5" t="n">
         <v>6788288</v>
@@ -1054,6 +1069,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Garnlav, återkommande i området.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1075,6 +1095,2260 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122566822</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461763</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6788475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122566827</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461879</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6788396</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122566809</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>461822</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6788353</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122566824</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6788470</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122566830</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>461991</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6788324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122566887</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6788470</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122566825</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>461843</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6788468</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122566835</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>461929</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6788278</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122566801</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>461945</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6788255</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122566832</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>461991</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6788292</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122566833</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>461972</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6788277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122566808</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90826</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>461872</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6788413</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122566834</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>461929</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6788262</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122566837</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>461917</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6788292</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122566816</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>461930</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6788270</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122566826</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>461846</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6788492</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122566805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122566831</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>462004</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6788320</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122566828</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>461923</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6788324</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122566838</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>461878</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6788313</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122566811</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>461936</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6788279</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122566829</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>461952</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6788327</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489274</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461988</v>
+        <v>461895</v>
       </c>
       <c r="R3" t="n">
         <v>6788288</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R5" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566822</v>
+        <v>122566816</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461763</v>
+        <v>461930</v>
       </c>
       <c r="R6" t="n">
-        <v>6788475</v>
+        <v>6788270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566827</v>
+        <v>122566834</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461879</v>
+        <v>461929</v>
       </c>
       <c r="R7" t="n">
-        <v>6788396</v>
+        <v>6788262</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566809</v>
+        <v>122566827</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461822</v>
+        <v>461879</v>
       </c>
       <c r="R8" t="n">
-        <v>6788353</v>
+        <v>6788396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566824</v>
+        <v>122566829</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461810</v>
+        <v>461952</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788327</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566830</v>
+        <v>122566833</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461991</v>
+        <v>461972</v>
       </c>
       <c r="R10" t="n">
-        <v>6788324</v>
+        <v>6788277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566887</v>
+        <v>122566805</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>74757</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461810</v>
+        <v>461848</v>
       </c>
       <c r="R11" t="n">
-        <v>6788470</v>
+        <v>6788429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566825</v>
+        <v>122566824</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461843</v>
+        <v>461810</v>
       </c>
       <c r="R12" t="n">
-        <v>6788468</v>
+        <v>6788470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566835</v>
+        <v>122566822</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461929</v>
+        <v>461763</v>
       </c>
       <c r="R13" t="n">
-        <v>6788278</v>
+        <v>6788475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566801</v>
+        <v>122566887</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461945</v>
+        <v>461810</v>
       </c>
       <c r="R14" t="n">
-        <v>6788255</v>
+        <v>6788470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566832</v>
+        <v>122566837</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2056,7 +2061,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461991</v>
+        <v>461917</v>
       </c>
       <c r="R15" t="n">
         <v>6788292</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566833</v>
+        <v>122566811</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,34 +2139,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461972</v>
+        <v>461936</v>
       </c>
       <c r="R16" t="n">
-        <v>6788277</v>
+        <v>6788279</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566808</v>
+        <v>122566835</v>
       </c>
       <c r="B17" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461872</v>
+        <v>461929</v>
       </c>
       <c r="R17" t="n">
-        <v>6788413</v>
+        <v>6788278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2332,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566834</v>
+        <v>122566832</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2362,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R18" t="n">
-        <v>6788262</v>
+        <v>6788292</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566837</v>
+        <v>122566825</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2464,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461917</v>
+        <v>461843</v>
       </c>
       <c r="R19" t="n">
-        <v>6788292</v>
+        <v>6788468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566816</v>
+        <v>122566838</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,39 +2552,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461930</v>
+        <v>461878</v>
       </c>
       <c r="R20" t="n">
-        <v>6788270</v>
+        <v>6788313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566826</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461846</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788492</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566805</v>
+        <v>122566809</v>
       </c>
       <c r="B22" t="n">
-        <v>74757</v>
+        <v>90859</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461848</v>
+        <v>461822</v>
       </c>
       <c r="R22" t="n">
-        <v>6788429</v>
+        <v>6788353</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566831</v>
+        <v>122566826</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462004</v>
+        <v>461846</v>
       </c>
       <c r="R23" t="n">
-        <v>6788320</v>
+        <v>6788492</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566838</v>
+        <v>122566801</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461878</v>
+        <v>461945</v>
       </c>
       <c r="R25" t="n">
-        <v>6788313</v>
+        <v>6788255</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566811</v>
+        <v>122566830</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,39 +3164,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461936</v>
+        <v>461991</v>
       </c>
       <c r="R26" t="n">
-        <v>6788279</v>
+        <v>6788324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566829</v>
+        <v>122566831</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461952</v>
+        <v>462004</v>
       </c>
       <c r="R27" t="n">
-        <v>6788327</v>
+        <v>6788320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R3" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489220</v>
+        <v>122489274</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461881</v>
+        <v>461895</v>
       </c>
       <c r="R5" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566816</v>
+        <v>122566830</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461930</v>
+        <v>461991</v>
       </c>
       <c r="R6" t="n">
-        <v>6788270</v>
+        <v>6788324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566834</v>
+        <v>122566838</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461929</v>
+        <v>461878</v>
       </c>
       <c r="R7" t="n">
-        <v>6788262</v>
+        <v>6788313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566827</v>
+        <v>122566825</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461879</v>
+        <v>461843</v>
       </c>
       <c r="R8" t="n">
-        <v>6788396</v>
+        <v>6788468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566829</v>
+        <v>122566832</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461952</v>
+        <v>461991</v>
       </c>
       <c r="R9" t="n">
-        <v>6788327</v>
+        <v>6788292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566833</v>
+        <v>122566816</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461972</v>
+        <v>461930</v>
       </c>
       <c r="R10" t="n">
-        <v>6788277</v>
+        <v>6788270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566805</v>
+        <v>122566837</v>
       </c>
       <c r="B11" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461848</v>
+        <v>461917</v>
       </c>
       <c r="R11" t="n">
-        <v>6788429</v>
+        <v>6788292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566824</v>
+        <v>122566835</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461810</v>
+        <v>461929</v>
       </c>
       <c r="R12" t="n">
-        <v>6788470</v>
+        <v>6788278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566822</v>
+        <v>122566831</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461763</v>
+        <v>462004</v>
       </c>
       <c r="R13" t="n">
-        <v>6788475</v>
+        <v>6788320</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566887</v>
+        <v>122566828</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461810</v>
+        <v>461923</v>
       </c>
       <c r="R14" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566837</v>
+        <v>122566822</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461917</v>
+        <v>461763</v>
       </c>
       <c r="R15" t="n">
-        <v>6788292</v>
+        <v>6788475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566811</v>
+        <v>122566833</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,39 +2139,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461936</v>
+        <v>461972</v>
       </c>
       <c r="R16" t="n">
-        <v>6788279</v>
+        <v>6788277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566835</v>
+        <v>122566826</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461929</v>
+        <v>461846</v>
       </c>
       <c r="R17" t="n">
-        <v>6788278</v>
+        <v>6788492</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566832</v>
+        <v>122566834</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461991</v>
+        <v>461929</v>
       </c>
       <c r="R18" t="n">
-        <v>6788292</v>
+        <v>6788262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566825</v>
+        <v>122566824</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461843</v>
+        <v>461810</v>
       </c>
       <c r="R19" t="n">
-        <v>6788468</v>
+        <v>6788470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566838</v>
+        <v>122566808</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461878</v>
+        <v>461872</v>
       </c>
       <c r="R20" t="n">
-        <v>6788313</v>
+        <v>6788413</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566801</v>
       </c>
       <c r="B21" t="n">
-        <v>90839</v>
+        <v>79274</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461945</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566809</v>
+        <v>122566887</v>
       </c>
       <c r="B22" t="n">
-        <v>90859</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461822</v>
+        <v>461810</v>
       </c>
       <c r="R22" t="n">
-        <v>6788353</v>
+        <v>6788470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566826</v>
+        <v>122566809</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461846</v>
+        <v>461822</v>
       </c>
       <c r="R23" t="n">
-        <v>6788492</v>
+        <v>6788353</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566828</v>
+        <v>122566827</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461923</v>
+        <v>461879</v>
       </c>
       <c r="R24" t="n">
-        <v>6788324</v>
+        <v>6788396</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566801</v>
+        <v>122566829</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461945</v>
+        <v>461952</v>
       </c>
       <c r="R25" t="n">
-        <v>6788255</v>
+        <v>6788327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566830</v>
+        <v>122566811</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,34 +3159,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461991</v>
+        <v>461936</v>
       </c>
       <c r="R26" t="n">
-        <v>6788324</v>
+        <v>6788279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566831</v>
+        <v>122566805</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462004</v>
+        <v>461848</v>
       </c>
       <c r="R27" t="n">
-        <v>6788320</v>
+        <v>6788429</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566816</v>
+        <v>122566837</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461930</v>
+        <v>461917</v>
       </c>
       <c r="R10" t="n">
-        <v>6788270</v>
+        <v>6788292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566837</v>
+        <v>122566816</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,34 +1624,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461917</v>
+        <v>461930</v>
       </c>
       <c r="R11" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566822</v>
+        <v>122566834</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461763</v>
+        <v>461929</v>
       </c>
       <c r="R15" t="n">
-        <v>6788475</v>
+        <v>6788262</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566833</v>
+        <v>122566822</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461972</v>
+        <v>461763</v>
       </c>
       <c r="R16" t="n">
-        <v>6788277</v>
+        <v>6788475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566826</v>
+        <v>122566833</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461846</v>
+        <v>461972</v>
       </c>
       <c r="R17" t="n">
-        <v>6788492</v>
+        <v>6788277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566834</v>
+        <v>122566826</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461929</v>
+        <v>461846</v>
       </c>
       <c r="R18" t="n">
-        <v>6788262</v>
+        <v>6788492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566808</v>
+        <v>122566801</v>
       </c>
       <c r="B20" t="n">
-        <v>90839</v>
+        <v>79274</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461872</v>
+        <v>461945</v>
       </c>
       <c r="R20" t="n">
-        <v>6788413</v>
+        <v>6788255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566801</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>90839</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461945</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788255</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566887</v>
+        <v>122566809</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>90859</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461810</v>
+        <v>461822</v>
       </c>
       <c r="R22" t="n">
-        <v>6788470</v>
+        <v>6788353</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566809</v>
+        <v>122566887</v>
       </c>
       <c r="B23" t="n">
-        <v>90859</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461822</v>
+        <v>461810</v>
       </c>
       <c r="R23" t="n">
-        <v>6788353</v>
+        <v>6788470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566830</v>
+        <v>122566833</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461991</v>
+        <v>461972</v>
       </c>
       <c r="R6" t="n">
-        <v>6788324</v>
+        <v>6788277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566838</v>
+        <v>122566831</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461878</v>
+        <v>462004</v>
       </c>
       <c r="R7" t="n">
-        <v>6788313</v>
+        <v>6788320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566825</v>
+        <v>122566827</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461843</v>
+        <v>461879</v>
       </c>
       <c r="R8" t="n">
-        <v>6788468</v>
+        <v>6788396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566832</v>
+        <v>122566887</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R9" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566837</v>
+        <v>122566826</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461917</v>
+        <v>461846</v>
       </c>
       <c r="R10" t="n">
-        <v>6788292</v>
+        <v>6788492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566816</v>
+        <v>122566837</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,39 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461930</v>
+        <v>461917</v>
       </c>
       <c r="R11" t="n">
-        <v>6788270</v>
+        <v>6788292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566835</v>
+        <v>122566828</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461929</v>
+        <v>461923</v>
       </c>
       <c r="R12" t="n">
-        <v>6788278</v>
+        <v>6788324</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566831</v>
+        <v>122566825</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462004</v>
+        <v>461843</v>
       </c>
       <c r="R13" t="n">
-        <v>6788320</v>
+        <v>6788468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566828</v>
+        <v>122566838</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461923</v>
+        <v>461878</v>
       </c>
       <c r="R14" t="n">
-        <v>6788324</v>
+        <v>6788313</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566834</v>
+        <v>122566811</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,34 +2032,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461929</v>
+        <v>461936</v>
       </c>
       <c r="R15" t="n">
-        <v>6788262</v>
+        <v>6788279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566822</v>
+        <v>122566824</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461763</v>
+        <v>461810</v>
       </c>
       <c r="R16" t="n">
-        <v>6788475</v>
+        <v>6788470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566833</v>
+        <v>122566805</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461972</v>
+        <v>461848</v>
       </c>
       <c r="R17" t="n">
-        <v>6788277</v>
+        <v>6788429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566826</v>
+        <v>122566822</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461846</v>
+        <v>461763</v>
       </c>
       <c r="R18" t="n">
-        <v>6788492</v>
+        <v>6788475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566824</v>
+        <v>122566830</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R19" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566801</v>
+        <v>122566834</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461945</v>
+        <v>461929</v>
       </c>
       <c r="R20" t="n">
-        <v>6788255</v>
+        <v>6788262</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566832</v>
       </c>
       <c r="B21" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461991</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
         <v>122566809</v>
       </c>
       <c r="B22" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566887</v>
+        <v>122566835</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461810</v>
+        <v>461929</v>
       </c>
       <c r="R23" t="n">
-        <v>6788470</v>
+        <v>6788278</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566827</v>
+        <v>122566829</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461879</v>
+        <v>461952</v>
       </c>
       <c r="R24" t="n">
-        <v>6788396</v>
+        <v>6788327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566829</v>
+        <v>122566816</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,34 +3057,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461952</v>
+        <v>461930</v>
       </c>
       <c r="R25" t="n">
-        <v>6788327</v>
+        <v>6788270</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566811</v>
+        <v>122566801</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>79274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,39 +3164,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461936</v>
+        <v>461945</v>
       </c>
       <c r="R26" t="n">
-        <v>6788279</v>
+        <v>6788255</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566805</v>
+        <v>122566808</v>
       </c>
       <c r="B27" t="n">
-        <v>74757</v>
+        <v>90833</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461848</v>
+        <v>461872</v>
       </c>
       <c r="R27" t="n">
-        <v>6788429</v>
+        <v>6788413</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566833</v>
+        <v>122566835</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461972</v>
+        <v>461929</v>
       </c>
       <c r="R6" t="n">
-        <v>6788277</v>
+        <v>6788278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566831</v>
+        <v>122566833</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462004</v>
+        <v>461972</v>
       </c>
       <c r="R7" t="n">
-        <v>6788320</v>
+        <v>6788277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566827</v>
+        <v>122566828</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461879</v>
+        <v>461923</v>
       </c>
       <c r="R8" t="n">
-        <v>6788396</v>
+        <v>6788324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566887</v>
+        <v>122566838</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461810</v>
+        <v>461878</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566826</v>
+        <v>122566824</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461846</v>
+        <v>461810</v>
       </c>
       <c r="R10" t="n">
-        <v>6788492</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566837</v>
+        <v>122566831</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461917</v>
+        <v>462004</v>
       </c>
       <c r="R11" t="n">
-        <v>6788292</v>
+        <v>6788320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566828</v>
+        <v>122566801</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461923</v>
+        <v>461945</v>
       </c>
       <c r="R12" t="n">
-        <v>6788324</v>
+        <v>6788255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566838</v>
+        <v>122566805</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461878</v>
+        <v>461848</v>
       </c>
       <c r="R14" t="n">
-        <v>6788313</v>
+        <v>6788429</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566811</v>
+        <v>122566808</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,39 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461936</v>
+        <v>461872</v>
       </c>
       <c r="R15" t="n">
-        <v>6788279</v>
+        <v>6788413</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566824</v>
+        <v>122566822</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461810</v>
+        <v>461763</v>
       </c>
       <c r="R16" t="n">
-        <v>6788470</v>
+        <v>6788475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566805</v>
+        <v>122566837</v>
       </c>
       <c r="B17" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461848</v>
+        <v>461917</v>
       </c>
       <c r="R17" t="n">
-        <v>6788429</v>
+        <v>6788292</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566822</v>
+        <v>122566829</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461763</v>
+        <v>461952</v>
       </c>
       <c r="R18" t="n">
-        <v>6788475</v>
+        <v>6788327</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566830</v>
+        <v>122566816</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461991</v>
+        <v>461930</v>
       </c>
       <c r="R19" t="n">
-        <v>6788324</v>
+        <v>6788270</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566835</v>
+        <v>122566830</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R23" t="n">
-        <v>6788278</v>
+        <v>6788324</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566829</v>
+        <v>122566887</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R24" t="n">
-        <v>6788327</v>
+        <v>6788470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566816</v>
+        <v>122566811</v>
       </c>
       <c r="B25" t="n">
         <v>57399</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461930</v>
+        <v>461936</v>
       </c>
       <c r="R25" t="n">
-        <v>6788270</v>
+        <v>6788279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566801</v>
+        <v>122566827</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461945</v>
+        <v>461879</v>
       </c>
       <c r="R26" t="n">
-        <v>6788255</v>
+        <v>6788396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566808</v>
+        <v>122566826</v>
       </c>
       <c r="B27" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461872</v>
+        <v>461846</v>
       </c>
       <c r="R27" t="n">
-        <v>6788413</v>
+        <v>6788492</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +790,7 @@
         <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489274</v>
+        <v>122566835</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461895</v>
+        <v>461929</v>
       </c>
       <c r="R5" t="n">
-        <v>6788288</v>
+        <v>6788278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566835</v>
+        <v>122566827</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461929</v>
+        <v>461879</v>
       </c>
       <c r="R6" t="n">
-        <v>6788278</v>
+        <v>6788396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566833</v>
+        <v>122566829</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461972</v>
+        <v>461952</v>
       </c>
       <c r="R7" t="n">
-        <v>6788277</v>
+        <v>6788327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566828</v>
+        <v>122566826</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461923</v>
+        <v>461846</v>
       </c>
       <c r="R8" t="n">
-        <v>6788324</v>
+        <v>6788492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566838</v>
+        <v>122566832</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461878</v>
+        <v>461991</v>
       </c>
       <c r="R9" t="n">
-        <v>6788313</v>
+        <v>6788292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566824</v>
+        <v>122566828</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461810</v>
+        <v>461923</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566831</v>
+        <v>122566811</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,34 +1619,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462004</v>
+        <v>461936</v>
       </c>
       <c r="R11" t="n">
-        <v>6788320</v>
+        <v>6788279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566801</v>
+        <v>122566834</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461945</v>
+        <v>461929</v>
       </c>
       <c r="R12" t="n">
-        <v>6788255</v>
+        <v>6788262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566825</v>
+        <v>122566816</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,34 +1828,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461843</v>
+        <v>461930</v>
       </c>
       <c r="R13" t="n">
-        <v>6788468</v>
+        <v>6788270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566805</v>
+        <v>122566822</v>
       </c>
       <c r="B14" t="n">
-        <v>74757</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461848</v>
+        <v>461763</v>
       </c>
       <c r="R14" t="n">
-        <v>6788429</v>
+        <v>6788475</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566808</v>
+        <v>122566824</v>
       </c>
       <c r="B15" t="n">
-        <v>90833</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461872</v>
+        <v>461810</v>
       </c>
       <c r="R15" t="n">
-        <v>6788413</v>
+        <v>6788470</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566822</v>
+        <v>122566831</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461763</v>
+        <v>462004</v>
       </c>
       <c r="R16" t="n">
-        <v>6788475</v>
+        <v>6788320</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566837</v>
+        <v>122566830</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461917</v>
+        <v>461991</v>
       </c>
       <c r="R17" t="n">
-        <v>6788292</v>
+        <v>6788324</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566829</v>
+        <v>122566808</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>90834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461952</v>
+        <v>461872</v>
       </c>
       <c r="R18" t="n">
-        <v>6788327</v>
+        <v>6788413</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566816</v>
+        <v>122566837</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,39 +2445,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461930</v>
+        <v>461917</v>
       </c>
       <c r="R19" t="n">
-        <v>6788270</v>
+        <v>6788292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566834</v>
+        <v>122566825</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461929</v>
+        <v>461843</v>
       </c>
       <c r="R20" t="n">
-        <v>6788262</v>
+        <v>6788468</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566832</v>
+        <v>122566887</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R21" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
         <v>122566809</v>
       </c>
       <c r="B22" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566830</v>
+        <v>122566801</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461991</v>
+        <v>461945</v>
       </c>
       <c r="R23" t="n">
-        <v>6788324</v>
+        <v>6788255</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566887</v>
+        <v>122566805</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>74758</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461848</v>
       </c>
       <c r="R24" t="n">
-        <v>6788470</v>
+        <v>6788429</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566811</v>
+        <v>122566833</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,39 +3057,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461936</v>
+        <v>461972</v>
       </c>
       <c r="R25" t="n">
-        <v>6788279</v>
+        <v>6788277</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566827</v>
+        <v>122566838</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3188,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461879</v>
+        <v>461878</v>
       </c>
       <c r="R26" t="n">
-        <v>6788396</v>
+        <v>6788313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566826</v>
+        <v>122488168</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,34 +3261,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461846</v>
+        <v>461923</v>
       </c>
       <c r="R27" t="n">
-        <v>6788492</v>
+        <v>6788245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3320,12 +3323,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3340,15 +3348,130 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122489274</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489220</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R3" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566835</v>
+        <v>122566830</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R5" t="n">
-        <v>6788278</v>
+        <v>6788324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566827</v>
+        <v>122566801</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461879</v>
+        <v>461945</v>
       </c>
       <c r="R6" t="n">
-        <v>6788396</v>
+        <v>6788255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566829</v>
+        <v>122566808</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461952</v>
+        <v>461872</v>
       </c>
       <c r="R7" t="n">
-        <v>6788327</v>
+        <v>6788413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566826</v>
+        <v>122566827</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461846</v>
+        <v>461879</v>
       </c>
       <c r="R8" t="n">
-        <v>6788492</v>
+        <v>6788396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566832</v>
+        <v>122566824</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R9" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566828</v>
+        <v>122566822</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461923</v>
+        <v>461763</v>
       </c>
       <c r="R10" t="n">
-        <v>6788324</v>
+        <v>6788475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566811</v>
+        <v>122566826</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,39 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461936</v>
+        <v>461846</v>
       </c>
       <c r="R11" t="n">
-        <v>6788279</v>
+        <v>6788492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566834</v>
+        <v>122566832</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R12" t="n">
-        <v>6788262</v>
+        <v>6788292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566816</v>
+        <v>122566833</v>
       </c>
       <c r="B13" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,39 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461930</v>
+        <v>461972</v>
       </c>
       <c r="R13" t="n">
-        <v>6788270</v>
+        <v>6788277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566822</v>
+        <v>122566838</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461763</v>
+        <v>461878</v>
       </c>
       <c r="R14" t="n">
-        <v>6788475</v>
+        <v>6788313</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566824</v>
+        <v>122566816</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,34 +2027,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461810</v>
+        <v>461930</v>
       </c>
       <c r="R15" t="n">
-        <v>6788470</v>
+        <v>6788270</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566831</v>
+        <v>122566887</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462004</v>
+        <v>461810</v>
       </c>
       <c r="R16" t="n">
-        <v>6788320</v>
+        <v>6788470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566830</v>
+        <v>122566831</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461991</v>
+        <v>462004</v>
       </c>
       <c r="R17" t="n">
-        <v>6788324</v>
+        <v>6788320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566808</v>
+        <v>122566828</v>
       </c>
       <c r="B18" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461872</v>
+        <v>461923</v>
       </c>
       <c r="R18" t="n">
-        <v>6788413</v>
+        <v>6788324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566837</v>
+        <v>122566835</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461917</v>
+        <v>461929</v>
       </c>
       <c r="R19" t="n">
-        <v>6788292</v>
+        <v>6788278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566825</v>
+        <v>122566829</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461843</v>
+        <v>461952</v>
       </c>
       <c r="R20" t="n">
-        <v>6788468</v>
+        <v>6788327</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566887</v>
+        <v>122566825</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461810</v>
+        <v>461843</v>
       </c>
       <c r="R21" t="n">
-        <v>6788470</v>
+        <v>6788468</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566809</v>
+        <v>122566805</v>
       </c>
       <c r="B22" t="n">
-        <v>90854</v>
+        <v>74761</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461822</v>
+        <v>461848</v>
       </c>
       <c r="R22" t="n">
-        <v>6788353</v>
+        <v>6788429</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566801</v>
+        <v>122566811</v>
       </c>
       <c r="B23" t="n">
-        <v>79275</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,34 +2848,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461945</v>
+        <v>461936</v>
       </c>
       <c r="R23" t="n">
-        <v>6788255</v>
+        <v>6788279</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566805</v>
+        <v>122566809</v>
       </c>
       <c r="B24" t="n">
-        <v>74758</v>
+        <v>90857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461848</v>
+        <v>461822</v>
       </c>
       <c r="R24" t="n">
-        <v>6788429</v>
+        <v>6788353</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566833</v>
+        <v>122566834</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461972</v>
+        <v>461929</v>
       </c>
       <c r="R25" t="n">
-        <v>6788277</v>
+        <v>6788262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566838</v>
+        <v>122566837</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461878</v>
+        <v>461917</v>
       </c>
       <c r="R26" t="n">
-        <v>6788313</v>
+        <v>6788292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566830</v>
+        <v>122566837</v>
       </c>
       <c r="B5" t="n">
         <v>78660</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461991</v>
+        <v>461917</v>
       </c>
       <c r="R5" t="n">
-        <v>6788324</v>
+        <v>6788292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566801</v>
+        <v>122566822</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461945</v>
+        <v>461763</v>
       </c>
       <c r="R6" t="n">
-        <v>6788255</v>
+        <v>6788475</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566808</v>
+        <v>122566816</v>
       </c>
       <c r="B7" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1211,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461872</v>
+        <v>461930</v>
       </c>
       <c r="R7" t="n">
-        <v>6788413</v>
+        <v>6788270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566827</v>
+        <v>122566835</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461879</v>
+        <v>461929</v>
       </c>
       <c r="R8" t="n">
-        <v>6788396</v>
+        <v>6788278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566824</v>
+        <v>122566830</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R9" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566822</v>
+        <v>122566831</v>
       </c>
       <c r="B10" t="n">
         <v>78660</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461763</v>
+        <v>462004</v>
       </c>
       <c r="R10" t="n">
-        <v>6788475</v>
+        <v>6788320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566826</v>
+        <v>122566828</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461846</v>
+        <v>461923</v>
       </c>
       <c r="R11" t="n">
-        <v>6788492</v>
+        <v>6788324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566832</v>
+        <v>122566833</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461991</v>
+        <v>461972</v>
       </c>
       <c r="R12" t="n">
-        <v>6788292</v>
+        <v>6788277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566833</v>
+        <v>122566809</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461972</v>
+        <v>461822</v>
       </c>
       <c r="R13" t="n">
-        <v>6788277</v>
+        <v>6788353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566838</v>
+        <v>122566805</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461878</v>
+        <v>461848</v>
       </c>
       <c r="R14" t="n">
-        <v>6788313</v>
+        <v>6788429</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566816</v>
+        <v>122566825</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,39 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461930</v>
+        <v>461843</v>
       </c>
       <c r="R15" t="n">
-        <v>6788270</v>
+        <v>6788468</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566887</v>
+        <v>122566832</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R16" t="n">
-        <v>6788470</v>
+        <v>6788292</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566831</v>
+        <v>122566811</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,34 +2236,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462004</v>
+        <v>461936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788320</v>
+        <v>6788279</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566828</v>
+        <v>122566801</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461923</v>
+        <v>461945</v>
       </c>
       <c r="R18" t="n">
-        <v>6788324</v>
+        <v>6788255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566835</v>
+        <v>122566826</v>
       </c>
       <c r="B19" t="n">
         <v>78660</v>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461929</v>
+        <v>461846</v>
       </c>
       <c r="R19" t="n">
-        <v>6788278</v>
+        <v>6788492</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566829</v>
+        <v>122566824</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R20" t="n">
-        <v>6788327</v>
+        <v>6788470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566825</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461843</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788468</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566805</v>
+        <v>122566834</v>
       </c>
       <c r="B22" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461848</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>6788429</v>
+        <v>6788262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566811</v>
+        <v>122566827</v>
       </c>
       <c r="B23" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,39 +2853,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461936</v>
+        <v>461879</v>
       </c>
       <c r="R23" t="n">
-        <v>6788279</v>
+        <v>6788396</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566809</v>
+        <v>122566829</v>
       </c>
       <c r="B24" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461822</v>
+        <v>461952</v>
       </c>
       <c r="R24" t="n">
-        <v>6788353</v>
+        <v>6788327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566834</v>
+        <v>122566838</v>
       </c>
       <c r="B25" t="n">
         <v>78660</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461929</v>
+        <v>461878</v>
       </c>
       <c r="R25" t="n">
-        <v>6788262</v>
+        <v>6788313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566837</v>
+        <v>122566887</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R26" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566832</v>
+        <v>122566811</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,34 +2134,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461991</v>
+        <v>461936</v>
       </c>
       <c r="R16" t="n">
-        <v>6788292</v>
+        <v>6788279</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566811</v>
+        <v>122566832</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,39 +2241,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461936</v>
+        <v>461991</v>
       </c>
       <c r="R17" t="n">
-        <v>6788279</v>
+        <v>6788292</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566834</v>
       </c>
       <c r="B21" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461929</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566834</v>
+        <v>122566808</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461929</v>
+        <v>461872</v>
       </c>
       <c r="R22" t="n">
-        <v>6788262</v>
+        <v>6788413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566822</v>
+        <v>122566816</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461763</v>
+        <v>461930</v>
       </c>
       <c r="R6" t="n">
-        <v>6788475</v>
+        <v>6788270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566816</v>
+        <v>122566822</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,39 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461930</v>
+        <v>461763</v>
       </c>
       <c r="R7" t="n">
-        <v>6788270</v>
+        <v>6788475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566834</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788262</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566808</v>
+        <v>122566834</v>
       </c>
       <c r="B22" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461872</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>6788413</v>
+        <v>6788262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566811</v>
+        <v>122566832</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,39 +2134,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461936</v>
+        <v>461991</v>
       </c>
       <c r="R16" t="n">
-        <v>6788279</v>
+        <v>6788292</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566832</v>
+        <v>122566811</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,34 +2236,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461991</v>
+        <v>461936</v>
       </c>
       <c r="R17" t="n">
-        <v>6788292</v>
+        <v>6788279</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3363,7 +3363,7 @@
         <v>122489274</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566805</v>
+        <v>122566808</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461848</v>
+        <v>461872</v>
       </c>
       <c r="R9" t="n">
-        <v>6788429</v>
+        <v>6788413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566808</v>
+        <v>122566805</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461872</v>
+        <v>461848</v>
       </c>
       <c r="R10" t="n">
-        <v>6788413</v>
+        <v>6788429</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566808</v>
+        <v>122566805</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461872</v>
+        <v>461848</v>
       </c>
       <c r="R9" t="n">
-        <v>6788413</v>
+        <v>6788429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566805</v>
+        <v>122566808</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461848</v>
+        <v>461872</v>
       </c>
       <c r="R10" t="n">
-        <v>6788429</v>
+        <v>6788413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566887</v>
+        <v>122566801</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>79380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2742,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461810</v>
+        <v>461945</v>
       </c>
       <c r="R22" t="n">
-        <v>6788470</v>
+        <v>6788255</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566801</v>
+        <v>122566830</v>
       </c>
       <c r="B23" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461945</v>
+        <v>461991</v>
       </c>
       <c r="R23" t="n">
-        <v>6788255</v>
+        <v>6788324</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566830</v>
+        <v>122566887</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,25 +2946,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R24" t="n">
-        <v>6788324</v>
+        <v>6788470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +790,7 @@
         <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566837</v>
+        <v>122566816</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461917</v>
+        <v>461930</v>
       </c>
       <c r="R5" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566828</v>
+        <v>122566837</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461923</v>
+        <v>461917</v>
       </c>
       <c r="R6" t="n">
-        <v>6788324</v>
+        <v>6788292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566816</v>
+        <v>122566822</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,39 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461930</v>
+        <v>461763</v>
       </c>
       <c r="R7" t="n">
-        <v>6788270</v>
+        <v>6788475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566838</v>
+        <v>122566809</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>90964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461878</v>
+        <v>461822</v>
       </c>
       <c r="R8" t="n">
-        <v>6788313</v>
+        <v>6788353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566805</v>
+        <v>122566826</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461848</v>
+        <v>461846</v>
       </c>
       <c r="R9" t="n">
-        <v>6788429</v>
+        <v>6788492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566808</v>
+        <v>122566887</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461872</v>
+        <v>461810</v>
       </c>
       <c r="R10" t="n">
-        <v>6788413</v>
+        <v>6788470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566809</v>
+        <v>122566831</v>
       </c>
       <c r="B11" t="n">
-        <v>90960</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461822</v>
+        <v>462004</v>
       </c>
       <c r="R11" t="n">
-        <v>6788353</v>
+        <v>6788320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566824</v>
+        <v>122566834</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461810</v>
+        <v>461929</v>
       </c>
       <c r="R12" t="n">
-        <v>6788470</v>
+        <v>6788262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566834</v>
+        <v>122566833</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461929</v>
+        <v>461972</v>
       </c>
       <c r="R13" t="n">
-        <v>6788262</v>
+        <v>6788277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566833</v>
+        <v>122566829</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461972</v>
+        <v>461952</v>
       </c>
       <c r="R14" t="n">
-        <v>6788277</v>
+        <v>6788327</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566827</v>
+        <v>122566835</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461879</v>
+        <v>461929</v>
       </c>
       <c r="R15" t="n">
-        <v>6788396</v>
+        <v>6788278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566831</v>
+        <v>122566825</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462004</v>
+        <v>461843</v>
       </c>
       <c r="R16" t="n">
-        <v>6788320</v>
+        <v>6788468</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566832</v>
+        <v>122566801</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461991</v>
+        <v>461945</v>
       </c>
       <c r="R17" t="n">
-        <v>6788292</v>
+        <v>6788255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566826</v>
+        <v>122566828</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461846</v>
+        <v>461923</v>
       </c>
       <c r="R18" t="n">
-        <v>6788492</v>
+        <v>6788324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566825</v>
+        <v>122566830</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461843</v>
+        <v>461991</v>
       </c>
       <c r="R19" t="n">
-        <v>6788468</v>
+        <v>6788324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566822</v>
+        <v>122566824</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461763</v>
+        <v>461810</v>
       </c>
       <c r="R20" t="n">
-        <v>6788475</v>
+        <v>6788470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566835</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461929</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788278</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566801</v>
+        <v>122566832</v>
       </c>
       <c r="B22" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461945</v>
+        <v>461991</v>
       </c>
       <c r="R22" t="n">
-        <v>6788255</v>
+        <v>6788292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566830</v>
+        <v>122566811</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,34 +2848,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461991</v>
+        <v>461936</v>
       </c>
       <c r="R23" t="n">
-        <v>6788324</v>
+        <v>6788279</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566887</v>
+        <v>122566838</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461878</v>
       </c>
       <c r="R24" t="n">
-        <v>6788470</v>
+        <v>6788313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566829</v>
+        <v>122566805</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461952</v>
+        <v>461848</v>
       </c>
       <c r="R25" t="n">
-        <v>6788327</v>
+        <v>6788429</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566811</v>
+        <v>122566827</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,39 +3159,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461936</v>
+        <v>461879</v>
       </c>
       <c r="R26" t="n">
-        <v>6788279</v>
+        <v>6788396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566816</v>
+        <v>122566833</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461930</v>
+        <v>461972</v>
       </c>
       <c r="R5" t="n">
-        <v>6788270</v>
+        <v>6788277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566822</v>
+        <v>122566887</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461763</v>
+        <v>461810</v>
       </c>
       <c r="R7" t="n">
-        <v>6788475</v>
+        <v>6788470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566809</v>
+        <v>122566828</v>
       </c>
       <c r="B8" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461822</v>
+        <v>461923</v>
       </c>
       <c r="R8" t="n">
-        <v>6788353</v>
+        <v>6788324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566826</v>
+        <v>122566834</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461846</v>
+        <v>461929</v>
       </c>
       <c r="R9" t="n">
-        <v>6788492</v>
+        <v>6788262</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566887</v>
+        <v>122566830</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R10" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566831</v>
+        <v>122566808</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462004</v>
+        <v>461872</v>
       </c>
       <c r="R11" t="n">
-        <v>6788320</v>
+        <v>6788413</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566834</v>
+        <v>122566825</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461929</v>
+        <v>461843</v>
       </c>
       <c r="R12" t="n">
-        <v>6788262</v>
+        <v>6788468</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566833</v>
+        <v>122566827</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461972</v>
+        <v>461879</v>
       </c>
       <c r="R13" t="n">
-        <v>6788277</v>
+        <v>6788396</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566829</v>
+        <v>122566824</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R14" t="n">
-        <v>6788327</v>
+        <v>6788470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566835</v>
+        <v>122566822</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461929</v>
+        <v>461763</v>
       </c>
       <c r="R15" t="n">
-        <v>6788278</v>
+        <v>6788475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566825</v>
+        <v>122566826</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2158,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461843</v>
+        <v>461846</v>
       </c>
       <c r="R16" t="n">
-        <v>6788468</v>
+        <v>6788492</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566828</v>
+        <v>122566811</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,34 +2333,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461923</v>
+        <v>461936</v>
       </c>
       <c r="R18" t="n">
-        <v>6788324</v>
+        <v>6788279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566830</v>
+        <v>122566832</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2467,7 +2467,7 @@
         <v>461991</v>
       </c>
       <c r="R19" t="n">
-        <v>6788324</v>
+        <v>6788292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566824</v>
+        <v>122566835</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461810</v>
+        <v>461929</v>
       </c>
       <c r="R20" t="n">
-        <v>6788470</v>
+        <v>6788278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566809</v>
       </c>
       <c r="B21" t="n">
-        <v>90944</v>
+        <v>90964</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461822</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788353</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566832</v>
+        <v>122566805</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461991</v>
+        <v>461848</v>
       </c>
       <c r="R22" t="n">
-        <v>6788292</v>
+        <v>6788429</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566811</v>
+        <v>122566829</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,39 +2848,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461936</v>
+        <v>461952</v>
       </c>
       <c r="R23" t="n">
-        <v>6788279</v>
+        <v>6788327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566838</v>
+        <v>122566816</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461878</v>
+        <v>461930</v>
       </c>
       <c r="R24" t="n">
-        <v>6788313</v>
+        <v>6788270</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566805</v>
+        <v>122566831</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461848</v>
+        <v>462004</v>
       </c>
       <c r="R25" t="n">
-        <v>6788429</v>
+        <v>6788320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566827</v>
+        <v>122566838</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461879</v>
+        <v>461878</v>
       </c>
       <c r="R26" t="n">
-        <v>6788396</v>
+        <v>6788313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566833</v>
+        <v>122566838</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461972</v>
+        <v>461878</v>
       </c>
       <c r="R5" t="n">
-        <v>6788277</v>
+        <v>6788313</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566837</v>
+        <v>122566809</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461917</v>
+        <v>461822</v>
       </c>
       <c r="R6" t="n">
-        <v>6788292</v>
+        <v>6788353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566887</v>
+        <v>122566811</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461810</v>
+        <v>461936</v>
       </c>
       <c r="R7" t="n">
-        <v>6788470</v>
+        <v>6788279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566828</v>
+        <v>122566835</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461923</v>
+        <v>461929</v>
       </c>
       <c r="R8" t="n">
-        <v>6788324</v>
+        <v>6788278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566830</v>
+        <v>122566831</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461991</v>
+        <v>462004</v>
       </c>
       <c r="R10" t="n">
-        <v>6788324</v>
+        <v>6788320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566808</v>
+        <v>122566829</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461872</v>
+        <v>461952</v>
       </c>
       <c r="R11" t="n">
-        <v>6788413</v>
+        <v>6788327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566825</v>
+        <v>122566805</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461843</v>
+        <v>461848</v>
       </c>
       <c r="R12" t="n">
-        <v>6788468</v>
+        <v>6788429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566827</v>
+        <v>122566832</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461879</v>
+        <v>461991</v>
       </c>
       <c r="R13" t="n">
-        <v>6788396</v>
+        <v>6788292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566824</v>
+        <v>122566808</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461810</v>
+        <v>461872</v>
       </c>
       <c r="R14" t="n">
-        <v>6788470</v>
+        <v>6788413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2317,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566811</v>
+        <v>122566825</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,39 +2338,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461936</v>
+        <v>461843</v>
       </c>
       <c r="R18" t="n">
-        <v>6788279</v>
+        <v>6788468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566832</v>
+        <v>122566816</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461991</v>
+        <v>461930</v>
       </c>
       <c r="R19" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566835</v>
+        <v>122566837</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461929</v>
+        <v>461917</v>
       </c>
       <c r="R20" t="n">
-        <v>6788278</v>
+        <v>6788292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566809</v>
+        <v>122566887</v>
       </c>
       <c r="B21" t="n">
-        <v>90964</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461822</v>
+        <v>461810</v>
       </c>
       <c r="R21" t="n">
-        <v>6788353</v>
+        <v>6788470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566805</v>
+        <v>122566827</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461848</v>
+        <v>461879</v>
       </c>
       <c r="R22" t="n">
-        <v>6788429</v>
+        <v>6788396</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566829</v>
+        <v>122566824</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R23" t="n">
-        <v>6788327</v>
+        <v>6788470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566816</v>
+        <v>122566830</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,39 +2955,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461930</v>
+        <v>461991</v>
       </c>
       <c r="R24" t="n">
-        <v>6788270</v>
+        <v>6788324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566831</v>
+        <v>122566828</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462004</v>
+        <v>461923</v>
       </c>
       <c r="R25" t="n">
-        <v>6788320</v>
+        <v>6788324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566838</v>
+        <v>122566833</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461878</v>
+        <v>461972</v>
       </c>
       <c r="R26" t="n">
-        <v>6788313</v>
+        <v>6788277</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566824</v>
+        <v>122566830</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R23" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566830</v>
+        <v>122566824</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R24" t="n">
-        <v>6788324</v>
+        <v>6788470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566830</v>
+        <v>122566824</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R23" t="n">
-        <v>6788324</v>
+        <v>6788470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566824</v>
+        <v>122566830</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R24" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566838</v>
+        <v>122566829</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461878</v>
+        <v>461952</v>
       </c>
       <c r="R5" t="n">
-        <v>6788313</v>
+        <v>6788327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566809</v>
+        <v>122566838</v>
       </c>
       <c r="B6" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461822</v>
+        <v>461878</v>
       </c>
       <c r="R6" t="n">
-        <v>6788353</v>
+        <v>6788313</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566811</v>
+        <v>122566830</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461936</v>
+        <v>461991</v>
       </c>
       <c r="R7" t="n">
-        <v>6788279</v>
+        <v>6788324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566835</v>
+        <v>122566828</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461929</v>
+        <v>461923</v>
       </c>
       <c r="R8" t="n">
-        <v>6788278</v>
+        <v>6788324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566834</v>
+        <v>122566801</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461929</v>
+        <v>461945</v>
       </c>
       <c r="R9" t="n">
-        <v>6788262</v>
+        <v>6788255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566831</v>
+        <v>122566825</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462004</v>
+        <v>461843</v>
       </c>
       <c r="R10" t="n">
-        <v>6788320</v>
+        <v>6788468</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566829</v>
+        <v>122566887</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R11" t="n">
-        <v>6788327</v>
+        <v>6788470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566805</v>
+        <v>122566837</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461848</v>
+        <v>461917</v>
       </c>
       <c r="R12" t="n">
-        <v>6788429</v>
+        <v>6788292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566808</v>
+        <v>122566826</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461872</v>
+        <v>461846</v>
       </c>
       <c r="R14" t="n">
-        <v>6788413</v>
+        <v>6788492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566822</v>
+        <v>122566827</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461763</v>
+        <v>461879</v>
       </c>
       <c r="R15" t="n">
-        <v>6788475</v>
+        <v>6788396</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566826</v>
+        <v>122566822</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2158,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461846</v>
+        <v>461763</v>
       </c>
       <c r="R16" t="n">
-        <v>6788492</v>
+        <v>6788475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566801</v>
+        <v>122566833</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461945</v>
+        <v>461972</v>
       </c>
       <c r="R17" t="n">
-        <v>6788255</v>
+        <v>6788277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566825</v>
+        <v>122566835</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461843</v>
+        <v>461929</v>
       </c>
       <c r="R18" t="n">
-        <v>6788468</v>
+        <v>6788278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566816</v>
+        <v>122566805</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,39 +2435,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461930</v>
+        <v>461848</v>
       </c>
       <c r="R19" t="n">
-        <v>6788270</v>
+        <v>6788429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566837</v>
+        <v>122566816</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,34 +2537,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461917</v>
+        <v>461930</v>
       </c>
       <c r="R20" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566887</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>90944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461810</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788470</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566827</v>
+        <v>122566834</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461879</v>
+        <v>461929</v>
       </c>
       <c r="R22" t="n">
-        <v>6788396</v>
+        <v>6788262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566830</v>
+        <v>122566831</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461991</v>
+        <v>462004</v>
       </c>
       <c r="R23" t="n">
-        <v>6788324</v>
+        <v>6788320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566824</v>
+        <v>122566811</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461936</v>
       </c>
       <c r="R24" t="n">
-        <v>6788470</v>
+        <v>6788279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566828</v>
+        <v>122566809</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461923</v>
+        <v>461822</v>
       </c>
       <c r="R25" t="n">
-        <v>6788324</v>
+        <v>6788353</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566833</v>
+        <v>122566824</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461972</v>
+        <v>461810</v>
       </c>
       <c r="R26" t="n">
-        <v>6788277</v>
+        <v>6788470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566887</v>
+        <v>122566837</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461810</v>
+        <v>461917</v>
       </c>
       <c r="R11" t="n">
-        <v>6788470</v>
+        <v>6788292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566837</v>
+        <v>122566832</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461917</v>
+        <v>461991</v>
       </c>
       <c r="R12" t="n">
         <v>6788292</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566832</v>
+        <v>122566887</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R13" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3363,7 +3363,7 @@
         <v>122489274</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3473,6 +3473,220 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124079435</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6788375</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124079560</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>461854</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6788321</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3687,6 +3687,1036 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124100914</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>461788</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6788461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124102499</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>461897</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6788354</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124103019</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124102323</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>461869</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124102093</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>658</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>461869</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124101056</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6788477</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124100759</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>461815</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6788432</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124103087</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124100321</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>461813</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6788469</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124099222</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6788394</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124079435</v>
+        <v>124079560</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3491,34 +3491,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461848</v>
+        <v>461854</v>
       </c>
       <c r="R29" t="n">
-        <v>6788375</v>
+        <v>6788321</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3556,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124079560</v>
+        <v>124079435</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,39 +3598,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R30" t="n">
-        <v>6788321</v>
+        <v>6788375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,6 +3658,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3689,10 +3689,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124100914</v>
+        <v>124101056</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,39 +3705,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461788</v>
+        <v>461781</v>
       </c>
       <c r="R31" t="n">
-        <v>6788461</v>
+        <v>6788477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3796,7 +3791,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124102499</v>
+        <v>124103087</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3836,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461897</v>
+        <v>461895</v>
       </c>
       <c r="R32" t="n">
-        <v>6788354</v>
+        <v>6788288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124103019</v>
+        <v>124100914</v>
       </c>
       <c r="B33" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,34 +3909,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461895</v>
+        <v>461788</v>
       </c>
       <c r="R33" t="n">
-        <v>6788288</v>
+        <v>6788461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124102323</v>
+        <v>124102429</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124102093</v>
+        <v>124100816</v>
       </c>
       <c r="B35" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461869</v>
+        <v>461815</v>
       </c>
       <c r="R35" t="n">
-        <v>6788429</v>
+        <v>6788432</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124101056</v>
+        <v>124103019</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4220,21 +4220,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R36" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124100759</v>
+        <v>124102093</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461815</v>
+        <v>461869</v>
       </c>
       <c r="R37" t="n">
-        <v>6788432</v>
+        <v>6788429</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4408,10 +4408,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124103087</v>
+        <v>124100321</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4424,21 +4424,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461895</v>
+        <v>461813</v>
       </c>
       <c r="R38" t="n">
-        <v>6788288</v>
+        <v>6788469</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4510,10 +4510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124100321</v>
+        <v>124102612</v>
       </c>
       <c r="B39" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461813</v>
+        <v>461897</v>
       </c>
       <c r="R39" t="n">
-        <v>6788469</v>
+        <v>6788354</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124079560</v>
+        <v>124101056</v>
       </c>
       <c r="B29" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3491,39 +3491,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461854</v>
+        <v>461781</v>
       </c>
       <c r="R29" t="n">
-        <v>6788321</v>
+        <v>6788477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,12 +3545,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,7 +3577,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124079435</v>
+        <v>124103087</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R30" t="n">
-        <v>6788375</v>
+        <v>6788288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,17 +3647,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3689,10 +3679,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124101056</v>
+        <v>124100914</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,34 +3695,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461781</v>
+        <v>461788</v>
       </c>
       <c r="R31" t="n">
-        <v>6788477</v>
+        <v>6788461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,7 +3786,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124103087</v>
+        <v>124102429</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3831,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R32" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124100914</v>
+        <v>124102612</v>
       </c>
       <c r="B33" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3909,39 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R33" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,7 +3990,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124102429</v>
+        <v>124100816</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -4034,16 +4024,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461869</v>
+        <v>461815</v>
       </c>
       <c r="R34" t="n">
-        <v>6788429</v>
+        <v>6788432</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,12 +4071,18 @@
           <t>2025-04-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4102,10 +4101,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124100816</v>
+        <v>124102093</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,34 +4117,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461815</v>
+        <v>461869</v>
       </c>
       <c r="R35" t="n">
-        <v>6788432</v>
+        <v>6788429</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,12 +4182,18 @@
           <t>2025-04-15</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4207,7 +4215,7 @@
         <v>124103019</v>
       </c>
       <c r="B36" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4220,24 +4228,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -4282,12 +4293,18 @@
           <t>2025-04-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4323,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124102093</v>
+        <v>124079435</v>
       </c>
       <c r="B37" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4322,34 +4339,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461869</v>
+        <v>461848</v>
       </c>
       <c r="R37" t="n">
-        <v>6788429</v>
+        <v>6788375</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,12 +4396,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,6 +4415,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4408,10 +4434,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124100321</v>
+        <v>124099222</v>
       </c>
       <c r="B38" t="n">
-        <v>91277</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4424,34 +4450,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461813</v>
+        <v>461848</v>
       </c>
       <c r="R38" t="n">
-        <v>6788469</v>
+        <v>6788394</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,6 +4518,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4510,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124102612</v>
+        <v>124079560</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4526,34 +4565,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461897</v>
+        <v>461854</v>
       </c>
       <c r="R39" t="n">
-        <v>6788354</v>
+        <v>6788321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4580,12 +4627,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4612,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124099222</v>
+        <v>124100321</v>
       </c>
       <c r="B40" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4628,39 +4680,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461848</v>
+        <v>461813</v>
       </c>
       <c r="R40" t="n">
-        <v>6788394</v>
+        <v>6788469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4695,12 +4745,18 @@
           <t>2025-04-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124101056</v>
+        <v>124103283</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R29" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124103087</v>
+        <v>124102323</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R30" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124100914</v>
+        <v>124102664</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3695,39 +3695,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R31" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,6 +3755,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3786,7 +3786,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124102429</v>
+        <v>124101056</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461869</v>
+        <v>461781</v>
       </c>
       <c r="R32" t="n">
-        <v>6788429</v>
+        <v>6788477</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124102612</v>
+        <v>124100914</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,34 +3904,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461897</v>
+        <v>461788</v>
       </c>
       <c r="R33" t="n">
-        <v>6788354</v>
+        <v>6788461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,7 +3995,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124100816</v>
+        <v>124100759</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -4073,7 +4078,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4212,10 +4217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124103019</v>
+        <v>124100321</v>
       </c>
       <c r="B36" t="n">
-        <v>91008</v>
+        <v>91277</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,21 +4233,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461895</v>
+        <v>461813</v>
       </c>
       <c r="R36" t="n">
-        <v>6788288</v>
+        <v>6788469</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,7 +4300,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124099222</v>
+        <v>124079560</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4450,16 +4455,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4482,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461848</v>
+        <v>461854</v>
       </c>
       <c r="R38" t="n">
-        <v>6788394</v>
+        <v>6788321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4512,17 +4517,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4549,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124079560</v>
+        <v>124099222</v>
       </c>
       <c r="B39" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,16 +4570,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4597,10 +4602,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R39" t="n">
-        <v>6788321</v>
+        <v>6788394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4627,17 +4632,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4664,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124100321</v>
+        <v>124103019</v>
       </c>
       <c r="B40" t="n">
-        <v>91277</v>
+        <v>91008</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4680,21 +4685,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4707,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461813</v>
+        <v>461895</v>
       </c>
       <c r="R40" t="n">
-        <v>6788469</v>
+        <v>6788288</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,7 +4752,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124102499</v>
+        <v>124101056</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R29" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124102429</v>
+        <v>124100914</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,34 +3593,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R30" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,7 +3684,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124103283</v>
+        <v>124102612</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3719,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461895</v>
+        <v>461897</v>
       </c>
       <c r="R31" t="n">
-        <v>6788288</v>
+        <v>6788354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3781,10 +3786,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124100914</v>
+        <v>124103087</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,39 +3802,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461788</v>
+        <v>461895</v>
       </c>
       <c r="R32" t="n">
-        <v>6788461</v>
+        <v>6788288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124101056</v>
+        <v>124102323</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461781</v>
+        <v>461869</v>
       </c>
       <c r="R33" t="n">
-        <v>6788477</v>
+        <v>6788429</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124100816</v>
+        <v>124103019</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,21 +4117,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461815</v>
+        <v>461895</v>
       </c>
       <c r="R35" t="n">
-        <v>6788432</v>
+        <v>6788288</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4212,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124079435</v>
+        <v>124079560</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,26 +4228,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4255,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461848</v>
+        <v>461854</v>
       </c>
       <c r="R36" t="n">
-        <v>6788375</v>
+        <v>6788321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,7 +4300,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4304,7 +4309,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4323,10 +4327,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124100321</v>
+        <v>124099222</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4339,26 +4343,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4366,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461813</v>
+        <v>461848</v>
       </c>
       <c r="R37" t="n">
-        <v>6788469</v>
+        <v>6788394</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,7 +4415,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4415,7 +4424,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4434,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124103019</v>
+        <v>124100759</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4450,21 +4458,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4477,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461895</v>
+        <v>461815</v>
       </c>
       <c r="R38" t="n">
-        <v>6788288</v>
+        <v>6788432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4517,7 +4525,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,10 +4553,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124079560</v>
+        <v>124100321</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,31 +4569,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4593,10 +4596,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461854</v>
+        <v>461813</v>
       </c>
       <c r="R39" t="n">
-        <v>6788321</v>
+        <v>6788469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,17 +4626,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,6 +4645,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4660,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124099222</v>
+        <v>124079435</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4676,31 +4680,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4711,7 +4710,7 @@
         <v>461848</v>
       </c>
       <c r="R40" t="n">
-        <v>6788394</v>
+        <v>6788375</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4738,17 +4737,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4757,6 +4756,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124101056</v>
+        <v>124103087</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R29" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124100914</v>
+        <v>124102499</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,39 +3593,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R30" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,7 +3679,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124102612</v>
+        <v>124101056</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R31" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,7 +3781,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124103087</v>
+        <v>124102429</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3826,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R32" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124102323</v>
+        <v>124100914</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,34 +3899,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R33" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,26 +4006,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4033,10 +4038,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R34" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4063,17 +4068,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4082,7 +4087,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4101,10 +4105,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124103019</v>
+        <v>124102093</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,21 +4121,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4148,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R35" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4184,7 +4188,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4212,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124079560</v>
+        <v>124100816</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,31 +4232,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4260,10 +4259,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461854</v>
+        <v>461815</v>
       </c>
       <c r="R36" t="n">
-        <v>6788321</v>
+        <v>6788432</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,17 +4289,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4309,6 +4308,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124099222</v>
+        <v>124100321</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4343,31 +4343,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461848</v>
+        <v>461813</v>
       </c>
       <c r="R37" t="n">
-        <v>6788394</v>
+        <v>6788469</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4415,7 +4410,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4424,6 +4419,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4442,7 +4438,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124100759</v>
+        <v>124079435</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4485,10 +4481,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461815</v>
+        <v>461848</v>
       </c>
       <c r="R38" t="n">
-        <v>6788432</v>
+        <v>6788375</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4515,17 +4511,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4553,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124100321</v>
+        <v>124103019</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461813</v>
+        <v>461895</v>
       </c>
       <c r="R39" t="n">
-        <v>6788469</v>
+        <v>6788288</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4636,7 +4632,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4664,10 +4660,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124079435</v>
+        <v>124099222</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4680,26 +4676,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4710,7 +4711,7 @@
         <v>461848</v>
       </c>
       <c r="R40" t="n">
-        <v>6788375</v>
+        <v>6788394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,17 +4738,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4756,7 +4757,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124103087</v>
+        <v>124102429</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R29" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124102499</v>
+        <v>124102612</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124101056</v>
+        <v>124103283</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R31" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124102429</v>
+        <v>124100914</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,34 +3797,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R32" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124100914</v>
+        <v>124101056</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,39 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461788</v>
+        <v>461781</v>
       </c>
       <c r="R33" t="n">
-        <v>6788461</v>
+        <v>6788477</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124102093</v>
+        <v>124079435</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461869</v>
+        <v>461848</v>
       </c>
       <c r="R35" t="n">
-        <v>6788429</v>
+        <v>6788375</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,17 +4178,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,10 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124100816</v>
+        <v>124099222</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4232,26 +4232,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4259,10 +4264,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461815</v>
+        <v>461848</v>
       </c>
       <c r="R36" t="n">
-        <v>6788432</v>
+        <v>6788394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,7 +4304,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4308,7 +4313,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4327,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124100321</v>
+        <v>124103019</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4343,21 +4347,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,10 +4374,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461813</v>
+        <v>461895</v>
       </c>
       <c r="R37" t="n">
-        <v>6788469</v>
+        <v>6788288</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4410,7 +4414,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4438,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124079435</v>
+        <v>124100321</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,21 +4458,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461848</v>
+        <v>461813</v>
       </c>
       <c r="R38" t="n">
-        <v>6788375</v>
+        <v>6788469</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4515,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4549,10 +4553,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124103019</v>
+        <v>124102093</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4596,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R39" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4632,7 +4636,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4660,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124099222</v>
+        <v>124100816</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4676,31 +4680,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4708,10 +4707,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461848</v>
+        <v>461815</v>
       </c>
       <c r="R40" t="n">
-        <v>6788394</v>
+        <v>6788432</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4748,7 +4747,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4757,6 +4756,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124102429</v>
+        <v>124102664</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461869</v>
+        <v>461897</v>
       </c>
       <c r="R29" t="n">
-        <v>6788429</v>
+        <v>6788354</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,6 +3551,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3577,7 +3582,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124102612</v>
+        <v>124101056</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R30" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,10 +3786,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124100914</v>
+        <v>124102429</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,39 +3802,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461788</v>
+        <v>461869</v>
       </c>
       <c r="R32" t="n">
-        <v>6788461</v>
+        <v>6788429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124101056</v>
+        <v>124100914</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,34 +3904,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461781</v>
+        <v>461788</v>
       </c>
       <c r="R33" t="n">
-        <v>6788477</v>
+        <v>6788461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124079560</v>
+        <v>124099222</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,16 +4011,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4038,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R34" t="n">
-        <v>6788321</v>
+        <v>6788394</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4068,17 +4073,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4105,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124079435</v>
+        <v>124103019</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4121,21 +4126,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4148,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R35" t="n">
-        <v>6788375</v>
+        <v>6788288</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,17 +4183,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,10 +4221,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124099222</v>
+        <v>124079435</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4232,31 +4237,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>461848</v>
       </c>
       <c r="R36" t="n">
-        <v>6788394</v>
+        <v>6788375</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,17 +4294,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4313,6 +4313,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4332,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124103019</v>
+        <v>124079560</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,26 +4348,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4374,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461895</v>
+        <v>461854</v>
       </c>
       <c r="R37" t="n">
-        <v>6788288</v>
+        <v>6788321</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4404,17 +4410,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4423,7 +4429,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4664,7 +4669,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124100816</v>
+        <v>124100759</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4747,7 +4752,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124102664</v>
+        <v>124103283</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461897</v>
+        <v>461895</v>
       </c>
       <c r="R29" t="n">
-        <v>6788354</v>
+        <v>6788288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3551,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124101056</v>
+        <v>124100914</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,34 +3593,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461781</v>
+        <v>461788</v>
       </c>
       <c r="R30" t="n">
-        <v>6788477</v>
+        <v>6788461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124103283</v>
+        <v>124101056</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461895</v>
+        <v>461781</v>
       </c>
       <c r="R31" t="n">
-        <v>6788288</v>
+        <v>6788477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124102429</v>
+        <v>124102323</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124100914</v>
+        <v>124102612</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,39 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R33" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3995,10 +3990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124099222</v>
+        <v>124103019</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4011,31 +4006,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4043,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R34" t="n">
-        <v>6788394</v>
+        <v>6788288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,7 +4073,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4092,6 +4082,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4110,10 +4101,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124103019</v>
+        <v>124100321</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,21 +4117,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461895</v>
+        <v>461813</v>
       </c>
       <c r="R35" t="n">
-        <v>6788288</v>
+        <v>6788469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4193,7 +4184,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4447,7 +4438,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124100321</v>
+        <v>124102093</v>
       </c>
       <c r="B38" t="n">
         <v>91299</v>
@@ -4490,10 +4481,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461813</v>
+        <v>461869</v>
       </c>
       <c r="R38" t="n">
-        <v>6788469</v>
+        <v>6788429</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4530,7 +4521,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4558,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124102093</v>
+        <v>124099222</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4574,26 +4565,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4601,10 +4597,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461869</v>
+        <v>461848</v>
       </c>
       <c r="R39" t="n">
-        <v>6788429</v>
+        <v>6788394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,7 +4637,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4650,7 +4646,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124103283</v>
+        <v>124102664</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461895</v>
+        <v>461897</v>
       </c>
       <c r="R29" t="n">
-        <v>6788288</v>
+        <v>6788354</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,6 +3551,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,7 +3893,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124102612</v>
+        <v>124103087</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3928,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461897</v>
+        <v>461895</v>
       </c>
       <c r="R33" t="n">
-        <v>6788354</v>
+        <v>6788288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124103019</v>
+        <v>124079560</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,26 +4011,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4033,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461895</v>
+        <v>461854</v>
       </c>
       <c r="R34" t="n">
-        <v>6788288</v>
+        <v>6788321</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4063,17 +4073,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4082,7 +4092,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4101,10 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124100321</v>
+        <v>124099222</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,26 +4126,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4144,10 +4158,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461813</v>
+        <v>461848</v>
       </c>
       <c r="R35" t="n">
-        <v>6788469</v>
+        <v>6788394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4184,7 +4198,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4193,7 +4207,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4212,10 +4225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124079435</v>
+        <v>124103019</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,21 +4241,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4268,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R36" t="n">
-        <v>6788375</v>
+        <v>6788288</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,17 +4298,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4323,10 +4336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124079560</v>
+        <v>124102093</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4339,31 +4352,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4371,10 +4379,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461854</v>
+        <v>461869</v>
       </c>
       <c r="R37" t="n">
-        <v>6788321</v>
+        <v>6788429</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,17 +4409,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,6 +4428,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4438,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124102093</v>
+        <v>124079435</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,10 +4490,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461869</v>
+        <v>461848</v>
       </c>
       <c r="R38" t="n">
-        <v>6788429</v>
+        <v>6788375</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,17 +4520,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4549,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124099222</v>
+        <v>124100321</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,31 +4574,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4597,10 +4601,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461848</v>
+        <v>461813</v>
       </c>
       <c r="R39" t="n">
-        <v>6788394</v>
+        <v>6788469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,7 +4641,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,6 +4650,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124102664</v>
+        <v>124100914</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3491,34 +3491,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461897</v>
+        <v>461788</v>
       </c>
       <c r="R29" t="n">
-        <v>6788354</v>
+        <v>6788461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3556,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124100914</v>
+        <v>124103087</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,39 +3598,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461788</v>
+        <v>461895</v>
       </c>
       <c r="R30" t="n">
-        <v>6788461</v>
+        <v>6788288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,7 +3684,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124101056</v>
+        <v>124102429</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461781</v>
+        <v>461869</v>
       </c>
       <c r="R31" t="n">
-        <v>6788477</v>
+        <v>6788429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,7 +3786,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124102323</v>
+        <v>124102664</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3831,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461869</v>
+        <v>461897</v>
       </c>
       <c r="R32" t="n">
-        <v>6788429</v>
+        <v>6788354</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,6 +3862,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3893,7 +3893,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124103087</v>
+        <v>124101056</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461895</v>
+        <v>461781</v>
       </c>
       <c r="R33" t="n">
-        <v>6788288</v>
+        <v>6788477</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124079560</v>
+        <v>124100321</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4011,31 +4011,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4043,10 +4038,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461854</v>
+        <v>461813</v>
       </c>
       <c r="R34" t="n">
-        <v>6788321</v>
+        <v>6788469</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,17 +4068,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4092,6 +4087,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4110,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124099222</v>
+        <v>124103019</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,31 +4122,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4158,10 +4149,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R35" t="n">
-        <v>6788394</v>
+        <v>6788288</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4198,7 +4189,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4207,6 +4198,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124103019</v>
+        <v>124099222</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,26 +4233,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4268,10 +4265,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461895</v>
+        <v>461848</v>
       </c>
       <c r="R36" t="n">
-        <v>6788288</v>
+        <v>6788394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4308,7 +4305,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4317,7 +4314,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4336,10 +4332,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4352,26 +4348,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R37" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4409,17 +4410,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4428,7 +4429,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124079435</v>
+        <v>124102093</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461848</v>
+        <v>461869</v>
       </c>
       <c r="R38" t="n">
-        <v>6788375</v>
+        <v>6788429</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4520,17 +4520,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4558,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124100321</v>
+        <v>124079435</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461813</v>
+        <v>461848</v>
       </c>
       <c r="R39" t="n">
-        <v>6788469</v>
+        <v>6788375</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4631,17 +4631,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -4106,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124103019</v>
+        <v>124079435</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461895</v>
+        <v>461848</v>
       </c>
       <c r="R35" t="n">
-        <v>6788288</v>
+        <v>6788375</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4217,10 +4217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124099222</v>
+        <v>124102093</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4233,31 +4233,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4265,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461848</v>
+        <v>461869</v>
       </c>
       <c r="R36" t="n">
-        <v>6788394</v>
+        <v>6788429</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4305,7 +4300,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4314,6 +4309,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4332,10 +4328,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124079560</v>
+        <v>124103019</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4348,31 +4344,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4380,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461854</v>
+        <v>461895</v>
       </c>
       <c r="R37" t="n">
-        <v>6788321</v>
+        <v>6788288</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4410,17 +4401,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4429,6 +4420,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4447,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,26 +4455,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4490,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R38" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4520,17 +4517,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4539,7 +4536,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124079435</v>
+        <v>124099222</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4574,26 +4570,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,7 +4605,7 @@
         <v>461848</v>
       </c>
       <c r="R39" t="n">
-        <v>6788375</v>
+        <v>6788394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4631,17 +4632,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4650,7 +4651,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -4669,7 +4669,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124100759</v>
+        <v>124100816</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -4669,7 +4669,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124100816</v>
+        <v>124100759</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2023 artfynd.xlsx
+++ b/artfynd/A 5064-2023 artfynd.xlsx
@@ -4672,7 +4672,7 @@
         <v>124100759</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
